--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE54"/>
+  <dimension ref="A1:AE53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 31577-2025</t>
+          <t>A 33166-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45833</v>
+        <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1106,145 +1106,145 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Jungfrulin
+Vippärt</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31577-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Sårläka
 Nästrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33166-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45126</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Jungfrulin
-Vippärt</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,46 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2032,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,49 +2065,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,14 +2117,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2141,8 +2136,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49123-2021</t>
+          <t>A 71317-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44453</v>
+        <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2456,8 +2456,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2500,7 +2505,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 71317-2021</t>
+          <t>A 71318-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2517,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2535,7 +2540,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2578,7 +2583,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 71318-2021</t>
+          <t>A 20641-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2592,10 +2597,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44539</v>
+        <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2607,13 +2612,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>9.1</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2656,7 +2656,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20641-2022</t>
+          <t>A 72097-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44700</v>
+        <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 72097-2021</t>
+          <t>A 3057-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44544</v>
+        <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3057-2022</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44582</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45835</v>
+        <v>45149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,8 +3123,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45596</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,8 +3201,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3254,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45754</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3328,14 +3333,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45054</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3347,13 +3352,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45120</v>
+        <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12.5</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45363</v>
+        <v>45596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45149</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3571,13 +3571,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45120</v>
+        <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46171</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45109</v>
+        <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44972</v>
+        <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4063,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45478</v>
+        <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4087,8 +4082,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45124</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44938</v>
+        <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,24 +4277,24 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>S 2392-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44918</v>
+        <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 2392-2024</t>
+          <t>S 378-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45468</v>
+        <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S 378-2025</t>
+          <t>S 2391-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45695</v>
+        <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S 2391-2024</t>
+          <t>S 2699-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45468</v>
+        <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S 2699-2024</t>
+          <t>S 377-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45482</v>
+        <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4642,7 +4642,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S 377-2025</t>
+          <t>S 373-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S 373-2025</t>
+          <t>S 370-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S 370-2025</t>
+          <t>S 2698-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45695</v>
+        <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4861,7 +4861,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S 2698-2024</t>
+          <t>S 374-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45482</v>
+        <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4931,10 +4931,10 @@
       </c>
       <c r="V52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S 374-2025</t>
+          <t>S 2043-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45695</v>
+        <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5003,79 +5003,6 @@
         <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>S 2043-2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,16 +1823,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1842,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1858,42 +1863,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1932,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,46 +1972,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2041,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2059,55 +2064,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,14 +2122,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44876</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,49 +2141,44 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2186,38 +2186,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2287,35 +2287,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45109</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>45417</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,13 +3123,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3184,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45596</v>
+        <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45478</v>
+        <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44938</v>
+        <v>45363</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44972</v>
+        <v>45124</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>45149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,8 +3863,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45417</v>
+        <v>44938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4063,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45054</v>
+        <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4080,11 +4085,6 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -4148,7 +4148,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44587</v>
+        <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>7.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,46 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44757</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2077,35 +2077,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45833</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2287,35 +2287,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45109</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>45149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,8 +3123,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3184,7 +3189,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3260,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44972</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46171</v>
+        <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46171</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45478</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45120</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45363</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45124</v>
+        <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45149</v>
+        <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,13 +3863,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44938</v>
+        <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4063,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44587</v>
+        <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4085,6 +4080,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -4148,7 +4148,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45835</v>
+        <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33166-2023</t>
+          <t>A 31577-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45126</v>
+        <v>45833</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1106,145 +1106,145 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Sårläka
+Nästrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33166-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Jungfrulin
 Vippärt</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31577-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Sårläka
-Nästrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,16 +1823,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1842,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1858,42 +1863,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1932,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,46 +1972,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,14 +2017,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2036,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2169,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45120</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,13 +3123,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3184,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44938</v>
+        <v>45149</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3571,8 +3571,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46171</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4063,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4082,13 +4087,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44587</v>
+        <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 31577-2025</t>
+          <t>A 33166-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45833</v>
+        <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1106,145 +1106,145 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Jungfrulin
+Vippärt</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31577-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Sårläka
 Nästrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33166-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45126</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Jungfrulin
-Vippärt</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,35 +1753,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1897,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,14 +1907,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1929,6 +1924,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1968,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -1976,38 +1976,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,49 +2070,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2178,46 +2178,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,8 +3128,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45754</v>
+        <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3206,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3260,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46171</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45149</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3571,13 +3571,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46171</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45120</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44587</v>
+        <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44918</v>
+        <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44876</v>
+        <v>46195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,49 +1926,44 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -1976,38 +1971,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,10 +2070,10 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45478</v>
+        <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3559,7 +3559,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>44938</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45775</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,10 +1823,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1830,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1842,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1854,50 +1859,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46195</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,16 +1928,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1951,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1960,49 +1961,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,14 +2017,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2036,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,41 +2247,41 @@
         </is>
       </c>
       <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45754</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,8 +2831,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2880,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2890,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,8 +2909,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2965,7 +2975,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3021,7 +3031,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3045,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45363</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3060,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3104,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3118,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45754</v>
+        <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,13 +3133,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45124</v>
+        <v>45417</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3279,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3328,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3342,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45596</v>
+        <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3401,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3415,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46171</v>
+        <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3431,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3474,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3488,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3504,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>45596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44938</v>
+        <v>45109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>45835</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45109</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45417</v>
+        <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>45124</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>44938</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4009,13 +4014,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4075,7 +4075,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44587</v>
+        <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45835</v>
+        <v>46171</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45775</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1835,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,46 +1854,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,14 +1907,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,17 +1926,22 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1952,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,50 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,49 +2070,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45833</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45754</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,13 +2831,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2880,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2890,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45054</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2909,13 +2904,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2975,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3045,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45363</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3060,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3104,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3118,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45417</v>
+        <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3133,8 +3128,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3328,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3342,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45517</v>
+        <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3415,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45120</v>
+        <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3431,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3474,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3488,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3504,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45596</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45109</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45835</v>
+        <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45124</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44938</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4075,7 +4075,7 @@
         <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46171</v>
+        <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46171</v>
+        <v>45835</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,35 +1758,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1902,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,14 +1912,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,13 +1931,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1968,46 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,55 +2064,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,41 +2247,41 @@
         </is>
       </c>
       <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3050,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3116,7 +3111,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3187,14 +3182,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3206,8 +3201,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45478</v>
+        <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>45363</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>45149</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3644,8 +3644,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46171</v>
+        <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45109</v>
+        <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45417</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4009,13 +4014,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44918</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45835</v>
+        <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45363</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>45149</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46171</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45363</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>45149</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,46 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44757</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2077,42 +2077,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,41 +2142,41 @@
         </is>
       </c>
       <c r="I16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
@@ -2186,38 +2186,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45754</v>
+        <v>45149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3182,14 +3182,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45054</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45835</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46171</v>
+        <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46171</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45363</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45149</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3644,13 +3644,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45120</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44587</v>
+        <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4063,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4087,8 +4082,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44918</v>
+        <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,16 +1823,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1842,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1858,42 +1863,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1932,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,46 +1972,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,14 +2017,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2031,13 +2036,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2169,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45120</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,13 +3123,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3184,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44938</v>
+        <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3778,7 +3783,7 @@
         <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46171</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4063,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4082,13 +4087,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44587</v>
+        <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1754,46 +1749,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45775</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1835,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,50 +1854,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2178,39 +2178,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 71318-2021</t>
+          <t>A 72097-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44539</v>
+        <v>44544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2534,13 +2534,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2583,7 +2578,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 20641-2022</t>
+          <t>A 3057-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2593,14 +2588,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44700</v>
+        <v>44582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2613,7 +2608,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2656,7 +2651,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 72097-2021</t>
+          <t>A 71318-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44544</v>
+        <v>44539</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2685,8 +2680,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>9.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3057-2022</t>
+          <t>A 20641-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44582</v>
+        <v>44700</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,8 +2831,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2880,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2890,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>44918</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2910,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2953,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2967,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2983,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3026,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3040,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>45109</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3056,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>44587</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3129,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45754</v>
+        <v>45417</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3201,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3274,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3332,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45754</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3352,8 +3347,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>45124</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,13 +3498,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45120</v>
+        <v>45363</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3630,14 +3625,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>45054</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3647,6 +3642,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3693,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46171</v>
+        <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>45596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>44938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45835</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>12.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>8.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44918</v>
+        <v>46171</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44757</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1749,46 +1754,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45775</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,10 +1823,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1830,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1842,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1854,46 +1859,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1932,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,46 +1972,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,14 +2017,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44876</v>
+        <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2029,11 +2034,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45833</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2178,39 +2178,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 72097-2021</t>
+          <t>A 71318-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44544</v>
+        <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2534,8 +2534,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2578,7 +2583,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3057-2022</t>
+          <t>A 20641-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2588,14 +2593,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44582</v>
+        <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2608,7 +2613,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2651,7 +2656,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 71318-2021</t>
+          <t>A 72097-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44539</v>
+        <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2680,13 +2685,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20641-2022</t>
+          <t>A 3057-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44700</v>
+        <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,13 +2831,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2880,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2890,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44918</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2910,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2953,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2967,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44972</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2983,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3026,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3040,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45109</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3056,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44587</v>
+        <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,8 +3123,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>7.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45517</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45754</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3347,13 +3352,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45124</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45363</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3625,14 +3630,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45054</v>
+        <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3644,13 +3649,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3710,7 @@
         <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45596</v>
+        <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44938</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45835</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45120</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>12.5</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46171</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46171</v>
+        <v>44918</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,35 +1753,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -1810,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1902,7 +1897,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1911,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1927,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1972,42 +1967,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,41 +2032,41 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
@@ -2081,38 +2076,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,14 +2117,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2141,8 +2136,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45754</v>
+        <v>45835</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,13 +3128,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45835</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3201,8 +3201,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>7.9</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3260,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,13 +3498,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3637,7 +3632,7 @@
         <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 24622-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45120</v>
+        <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44587</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3856,7 +3851,7 @@
         <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4063,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4087,8 +4082,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44918</v>
+        <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45835</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45835</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45417</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45695</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45695</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45482</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>46219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE53"/>
+  <dimension ref="A1:AE52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 33166-2023</t>
+          <t>A 31577-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45126</v>
+        <v>45833</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1106,145 +1106,145 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Sårläka
+Nästrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 33166-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Jungfrulin
 Vippärt</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31577-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Sårläka
-Nästrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,35 +1758,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1919,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2065,49 +2070,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,14 +2122,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,13 +2141,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3050,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45835</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3129,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3184,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44938</v>
+        <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46171</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24622-2026</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3705,7 +3710,7 @@
         <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45417</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45517</v>
+        <v>45124</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4063,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45054</v>
+        <v>44938</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4082,13 +4087,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,24 +4204,24 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>S 2392-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44587</v>
+        <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 2392-2024</t>
+          <t>S 378-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45468</v>
+        <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 378-2025</t>
+          <t>S 2391-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45695</v>
+        <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S 2391-2024</t>
+          <t>S 2699-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45468</v>
+        <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S 2699-2024</t>
+          <t>S 377-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45482</v>
+        <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S 377-2025</t>
+          <t>S 373-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4642,7 +4642,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S 373-2025</t>
+          <t>S 370-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S 370-2025</t>
+          <t>S 2698-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45695</v>
+        <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S 2698-2024</t>
+          <t>S 374-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45482</v>
+        <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4858,10 +4858,10 @@
       </c>
       <c r="V51" s="2" t="inlineStr"/>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S 374-2025</t>
+          <t>S 2043-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45695</v>
+        <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4930,79 +4930,6 @@
         <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>S 2043-2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 31577-2025</t>
+          <t>A 33166-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45833</v>
+        <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1106,145 +1106,145 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Gullklöver
+Jungfrulin
+Vippärt</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31577-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Sårläka
 Nästrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31577-2025 artfynd.xlsx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31577-2025 karta.png", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31577-2025 georefererad karta.tif", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31577-2025 FSC-klagomål.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31577-2025 FSC-klagomål mail.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31577-2025 tillsynsbegäran.docx", "A 31577-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31577-2025 tillsynsbegäran mail.docx", "A 31577-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 33166-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45126</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Gullklöver
-Jungfrulin
-Vippärt</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33166-2023 artfynd.xlsx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33166-2023 karta.png", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33166-2023 georefererad karta.tif", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33166-2023 FSC-klagomål.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33166-2023 FSC-klagomål mail.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33166-2023 tillsynsbegäran.docx", "A 33166-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33166-2023 tillsynsbegäran mail.docx", "A 33166-2023")</f>
         <v/>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,46 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2032,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,49 +2065,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,14 +2117,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2141,8 +2136,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>45835</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3129,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45754</v>
+        <v>46171</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3201,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45754</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3276,11 +3276,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45124</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,13 +3498,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45120</v>
+        <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46171</v>
+        <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
         <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44938</v>
+        <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45833</v>
+        <v>45775</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,7 +1823,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1827,10 +1832,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1845,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1854,39 +1859,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -1910,7 +1915,7 @@
         <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2076,38 +2081,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,14 +2122,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,13 +2141,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2178,46 +2178,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>44918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,8 +2904,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2965,7 +2970,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3040,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45363</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3055,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45835</v>
+        <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.9</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46171</v>
+        <v>45417</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45754</v>
+        <v>45149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45124</v>
+        <v>45835</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45417</v>
+        <v>45517</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45478</v>
+        <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44938</v>
+        <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45109</v>
+        <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45417</v>
+        <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,8 +3863,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4009,13 +4014,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44918</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45775</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1835,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,46 +1854,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,14 +1907,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,17 +1926,22 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1952,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,50 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,41 +2037,41 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44918</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45054</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,13 +2904,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2970,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3040,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45363</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3055,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45417</v>
+        <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,8 +3128,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3202,7 +3207,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3259,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45835</v>
+        <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45120</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44587</v>
+        <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45596</v>
+        <v>45109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>45417</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>45517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45754</v>
+        <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,13 +3863,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,14 +3917,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3941,8 +3936,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>45835</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,35 +1758,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1902,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,14 +1912,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,13 +1931,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1968,46 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2178,46 +2178,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,41 +2247,41 @@
         </is>
       </c>
       <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>44938</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>12.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45120</v>
+        <v>45363</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3050,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45754</v>
+        <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,13 +3123,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3177,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3187,14 +3177,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45124</v>
+        <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3240,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3254,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3269,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3332,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45596</v>
+        <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3391,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3405,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45478</v>
+        <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3421,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3464,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3494,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3537,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3551,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44972</v>
+        <v>45835</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3567,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3610,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3624,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45109</v>
+        <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3640,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3683,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3697,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45417</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3713,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3756,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3770,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45517</v>
+        <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3790,8 +3785,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46171</v>
+        <v>45054</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,8 +3863,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3917,14 +3922,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45054</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3936,13 +3941,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44918</v>
+        <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44587</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45835</v>
+        <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44938</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45363</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45417</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45835</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45054</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44938</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45363</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45417</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45149</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45517</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45835</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45054</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46171</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1754,46 +1749,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>46195</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1856,53 +1851,49 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44757</v>
+        <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,7 +1923,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1941,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1959,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1968,39 +1959,39 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -2024,7 +2015,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2103,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2117,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>44785</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,10 +2133,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2154,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2166,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2178,46 +2169,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2227,14 +2222,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44876</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2246,8 +2241,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,10 +2280,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44938</v>
+        <v>46171</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>8.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>44918</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12.5</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45363</v>
+        <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44918</v>
+        <v>45120</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45149</v>
+        <v>45120</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,13 +3269,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>12.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3313,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3327,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45517</v>
+        <v>45149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3347,8 +3342,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45120</v>
+        <v>45754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3420,8 +3420,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3478,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44587</v>
+        <v>45124</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3494,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3537,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3551,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45835</v>
+        <v>45417</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3567,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3627,7 +3632,7 @@
         <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3697,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3713,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3756,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3770,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45754</v>
+        <v>44938</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3785,13 +3790,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45054</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,13 +3863,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3994,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45478</v>
+        <v>45417</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4067,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>45517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4083,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4126,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4136,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46171</v>
+        <v>45054</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4160,8 +4155,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44757</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1749,46 +1754,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46195</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,16 +1823,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1842,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1851,49 +1856,53 @@
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45775</v>
+        <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,7 +1932,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1932,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1950,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1959,46 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45833</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2068,42 +2077,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44785</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2133,10 +2142,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2145,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2157,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2169,50 +2178,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2222,14 +2227,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44876</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2241,49 +2246,44 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46171</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44918</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44587</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45363</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45120</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,8 +3196,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3250,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45120</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3313,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3327,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45149</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3342,13 +3352,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3391,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3405,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45754</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3420,13 +3425,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45124</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45596</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45478</v>
+        <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44938</v>
+        <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3851,7 +3856,7 @@
         <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45109</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4067,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45517</v>
+        <v>44938</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4083,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4126,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4140,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45054</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4155,13 +4160,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45833</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1710,11 +1710,6 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1754,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
@@ -1762,38 +1757,38 @@
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45775</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1835,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1847,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1859,50 +1854,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2036,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2169,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2819,7 +2819,7 @@
         <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45835</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45363</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45754</v>
+        <v>45478</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3196,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3240,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3255,14 +3250,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45120</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3274,13 +3269,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3313,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3327,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>44938</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3343,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3386,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3400,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>45149</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,8 +3415,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3464,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>45754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3504,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45120</v>
+        <v>45124</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46171</v>
+        <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3783,7 +3778,7 @@
         <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44938</v>
+        <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45833</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1749,46 +1749,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1798,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,8 +1817,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1827,10 +1832,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1845,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1858,35 +1863,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1910,7 +1915,7 @@
         <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2002,7 +2007,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,14 +2017,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44876</v>
+        <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2029,11 +2034,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2175,49 +2175,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,8 +2831,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2892,7 +2897,7 @@
         <v>45835</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2967,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45363</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2983,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3026,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3040,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3056,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3129,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45478</v>
+        <v>45417</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3197,7 +3202,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3254,10 +3259,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3270,7 +3275,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3313,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3327,10 +3332,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44938</v>
+        <v>45149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3342,8 +3347,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3386,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3400,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45149</v>
+        <v>45120</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3415,13 +3425,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3478,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45754</v>
+        <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3493,13 +3498,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45124</v>
+        <v>45596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46171</v>
+        <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3644,8 +3644,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45109</v>
+        <v>46171</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4009,13 +4014,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44918</v>
+        <v>44938</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44587</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1798,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44876</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,22 +1817,17 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,46 +1854,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,14 +1907,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,17 +1926,22 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1952,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,50 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,41 +2037,41 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45054</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2831,13 +2831,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2880,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2894,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45835</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2910,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.9</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2970,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3040,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45363</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3055,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45417</v>
+        <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3128,8 +3128,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3186,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3202,7 +3207,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3259,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45517</v>
+        <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3275,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3347,13 +3352,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45120</v>
+        <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44587</v>
+        <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45596</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45754</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3644,13 +3644,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3710,7 +3705,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46171</v>
+        <v>45417</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3922,14 +3917,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3941,8 +3936,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45124</v>
+        <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44938</v>
+        <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>45835</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45417</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45835</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45417</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>44938</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45417</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45835</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45468</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45695</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45468</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45482</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45695</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45695</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE52"/>
+  <dimension ref="A1:AE56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,35 +1758,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1897,7 +1902,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,14 +1912,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44876</v>
+        <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,13 +1931,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1968,46 +1968,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,55 +2064,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2175,42 +2175,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>45833</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3050,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3116,7 +3111,7 @@
         <v>45754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3187,14 +3182,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3206,8 +3201,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45478</v>
+        <v>45149</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,8 +3425,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3474,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3488,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44938</v>
+        <v>45120</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3499,7 +3504,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3559,7 +3564,7 @@
         <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3705,7 +3710,7 @@
         <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3761,7 +3766,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3775,10 +3780,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3791,7 +3796,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3917,14 +3922,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3936,13 +3941,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44918</v>
+        <v>44938</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44587</v>
+        <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>45835</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,24 +4204,24 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 2392-2024</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45468</v>
+        <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,24 +4277,24 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 378-2025</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45695</v>
+        <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,24 +4350,24 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 2391-2024</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45468</v>
+        <v>46314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,24 +4423,24 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S 2699-2024</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45482</v>
+        <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S 377-2025</t>
+          <t>S 2392-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45695</v>
+        <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S 373-2025</t>
+          <t>S 378-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4642,7 +4642,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S 370-2025</t>
+          <t>S 2391-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45695</v>
+        <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S 2698-2024</t>
+          <t>S 2699-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S 374-2025</t>
+          <t>S 377-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4818,118 +4818,410 @@
         </is>
       </c>
       <c r="I51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S 373-2025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>45695</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S 370-2025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>45695</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S 2698-2024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>45482</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S 374-2025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>45695</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>3.1</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>S 2043-2026</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D56" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="E52" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>VÄRMDÖ</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
+      <c r="E56" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>VÄRMDÖ</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
         <v>0.5</v>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,46 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1916,10 +1907,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44757</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1932,16 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1956,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1972,42 +1963,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2032,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,55 +2059,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,14 +2117,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>44876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2141,8 +2136,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2175,10 +2175,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2186,38 +2186,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45833</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2287,35 +2287,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,8 +3050,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3099,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45754</v>
+        <v>45835</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,13 +3128,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3172,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3182,14 +3182,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45054</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45120</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45149</v>
+        <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3425,13 +3425,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3474,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3488,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45120</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3504,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>46171</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>8.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44972</v>
+        <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>45417</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45124</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44938</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44918</v>
+        <v>46314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45835</v>
+        <v>46314</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,14 +4360,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46314</v>
+        <v>44918</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46314</v>
+        <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45833</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,16 +1823,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1842,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1858,42 +1863,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1932,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1963,46 +1972,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2065,49 +2070,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,14 +2122,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2136,13 +2141,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2182,42 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2280,42 +2280,42 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45149</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3050,13 +3050,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3099,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45835</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3129,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3184,7 @@
         <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3245,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3255,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45124</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3274,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45596</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44938</v>
+        <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46171</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>46171</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
         <v>45109</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>45478</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3990,14 +3995,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4009,13 +4014,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46314</v>
+        <v>44938</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46314</v>
+        <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4360,14 +4360,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44918</v>
+        <v>46314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44587</v>
+        <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,14 +1798,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1822,17 +1817,22 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,43 +1859,39 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -1919,7 +1915,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2020,7 @@
         <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2108,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2138,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2151,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2169,55 +2165,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44785</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,16 +2243,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2271,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2280,42 +2276,46 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45417</v>
+        <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45417</v>
+        <v>45109</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45835</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45835</v>
+        <v>45417</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45754</v>
+        <v>45363</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3196,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3262,7 +3257,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3323,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3340,7 +3335,7 @@
         <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3348,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3391,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3406,14 +3401,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>44918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3421,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3464,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>44587</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,13 +3493,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3537,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3561,10 +3551,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45120</v>
+        <v>46171</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3577,7 +3567,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3620,7 +3610,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3634,10 +3624,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3650,7 +3640,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3693,7 +3683,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3697,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46171</v>
+        <v>46314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3713,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3756,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3770,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45109</v>
+        <v>46314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3796,7 +3786,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3829,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3843,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>46314</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3869,7 +3859,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3902,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3916,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45478</v>
+        <v>45120</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3932,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3975,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3999,10 +3989,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45124</v>
+        <v>45149</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4004,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4072,10 +4067,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44938</v>
+        <v>45754</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4087,8 +4082,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44918</v>
+        <v>45124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46314</v>
+        <v>45417</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46314</v>
+        <v>45596</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46314</v>
+        <v>45478</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46314</v>
+        <v>44938</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,8 +1712,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1753,42 +1758,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1803,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44876</v>
+        <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,22 +1822,17 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1859,46 +1859,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1928,41 +1932,41 @@
         </is>
       </c>
       <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
@@ -1972,38 +1976,38 @@
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2033,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2073,42 +2077,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2138,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2171,49 +2175,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44785</v>
+        <v>45775</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2243,10 +2247,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2255,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2267,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2279,43 +2283,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45109</v>
+        <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45835</v>
+        <v>46171</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45517</v>
+        <v>44938</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45363</v>
+        <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3250,14 +3250,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,13 +3269,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3313,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3327,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3348,7 +3343,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3391,7 +3386,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3401,14 +3396,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44918</v>
+        <v>45417</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3421,7 +3416,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3459,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3478,10 +3473,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44587</v>
+        <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3494,7 +3489,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3537,7 +3532,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3551,10 +3546,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46171</v>
+        <v>46314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3567,7 +3562,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3610,7 +3605,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3627,7 +3622,7 @@
         <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3640,7 +3635,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3683,7 +3678,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3700,7 +3695,7 @@
         <v>46314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3713,7 +3708,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3756,7 +3751,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3773,7 +3768,7 @@
         <v>46314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3786,7 +3781,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3829,7 +3824,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3843,10 +3838,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46314</v>
+        <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3859,7 +3854,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3902,7 +3897,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45120</v>
+        <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3931,8 +3926,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3985,14 +3985,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45149</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4006,11 +4006,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45754</v>
+        <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4082,13 +4082,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4126,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4140,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45124</v>
+        <v>45363</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4156,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4199,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4218,10 +4213,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4233,8 +4228,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45478</v>
+        <v>44587</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44938</v>
+        <v>45109</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45775</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>46171</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45124</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44938</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45417</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>46314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>46314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>46314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45363</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45149</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44587</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45109</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44876</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>46195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45775</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>46171</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45124</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44938</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>45417</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>46314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>46314</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>46314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45363</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45149</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44587</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45109</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1693,14 +1693,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1712,13 +1712,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1727,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1745,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1758,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44785</v>
+        <v>44757</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1823,16 +1818,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1847,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1863,39 +1858,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -1919,7 +1910,7 @@
         <v>46195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2015,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2112,7 +2103,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2117,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>44785</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,16 +2133,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2166,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2182,42 +2173,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2227,14 +2222,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45775</v>
+        <v>44876</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2246,8 +2241,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2287,35 +2287,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44972</v>
+        <v>44918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45478</v>
+        <v>44587</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46171</v>
+        <v>45363</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45124</v>
+        <v>45120</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44938</v>
+        <v>45120</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3177,14 +3177,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44918</v>
+        <v>45149</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,8 +3196,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3257,7 +3262,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3313,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3327,10 +3332,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45417</v>
+        <v>45754</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3342,8 +3347,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3386,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3400,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45417</v>
+        <v>45124</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3416,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3459,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3473,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45517</v>
+        <v>45417</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3489,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3532,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3546,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46314</v>
+        <v>45596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3562,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3605,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3619,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46314</v>
+        <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3635,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3678,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3692,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46314</v>
+        <v>44938</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3708,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3751,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3765,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46314</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3781,7 +3791,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3824,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3838,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45596</v>
+        <v>45109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3854,7 +3864,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3897,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3911,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45754</v>
+        <v>46171</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3926,13 +3936,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3975,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3985,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45054</v>
+        <v>45417</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4004,13 +4009,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45120</v>
+        <v>45517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>12.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45363</v>
+        <v>45054</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4155,8 +4155,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4199,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45149</v>
+        <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4228,13 +4233,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45120</v>
+        <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44587</v>
+        <v>46314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45109</v>
+        <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45775</v>
+        <v>44757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1749,46 +1749,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1798,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44757</v>
+        <v>44876</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,8 +1817,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1854,46 +1859,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1907,10 +1912,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46195</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1923,16 +1928,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1947,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1956,49 +1961,53 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,10 +2021,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45833</v>
+        <v>45775</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2037,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2037,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2055,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2064,46 +2073,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2117,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44785</v>
+        <v>45833</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2133,16 +2142,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2157,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2173,46 +2182,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2222,14 +2227,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44876</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2241,49 +2246,44 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2812,14 +2812,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44918</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44587</v>
+        <v>45754</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,8 +2904,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2953,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2958,14 +2963,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45363</v>
+        <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2977,8 +2982,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3031,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3031,14 +3041,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45120</v>
+        <v>44918</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3061,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3104,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3118,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45120</v>
+        <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3124,7 +3134,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3177,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3191,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,13 +3206,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3245,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3259,10 +3264,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45835</v>
+        <v>45517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3275,7 +3280,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45754</v>
+        <v>45120</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3347,13 +3352,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45124</v>
+        <v>45363</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,8 +3498,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3542,7 +3547,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3556,10 +3561,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45596</v>
+        <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3572,7 +3577,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45478</v>
+        <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3645,7 +3650,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3688,7 +3693,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3702,10 +3707,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44938</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3718,7 +3723,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3778,7 +3783,7 @@
         <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3834,7 +3839,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45109</v>
+        <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3864,7 +3869,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3907,7 +3912,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46171</v>
+        <v>45124</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3980,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45417</v>
+        <v>46314</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4010,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4053,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4067,10 +4072,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45517</v>
+        <v>46314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4083,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4126,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4136,14 +4141,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45054</v>
+        <v>44938</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4155,13 +4160,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46314</v>
+        <v>45835</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>7.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46314</v>
+        <v>46171</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44757</v>
+        <v>45833</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1753,42 +1753,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,14 +1798,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44876</v>
+        <v>45775</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1817,13 +1817,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1832,10 +1827,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1850,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1863,42 +1858,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1908,14 +1903,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44785</v>
+        <v>44876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1927,17 +1922,22 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,50 +1964,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2037,7 +2033,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2046,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2064,55 +2060,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45833</v>
+        <v>44757</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,7 +2138,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2182,42 +2178,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2231,10 +2227,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>44785</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2247,16 +2243,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2271,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2280,42 +2276,46 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>44938</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45754</v>
+        <v>45835</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2904,13 +2904,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2953,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2963,14 +2958,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45054</v>
+        <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2982,13 +2977,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3041,14 +3031,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44918</v>
+        <v>45109</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3061,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3121,7 +3111,7 @@
         <v>45417</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3167,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3191,10 +3181,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45417</v>
+        <v>45517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3207,7 +3197,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3250,7 +3240,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3260,14 +3250,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45517</v>
+        <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3279,8 +3269,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3323,7 +3318,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3337,10 +3332,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45120</v>
+        <v>45363</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3353,7 +3348,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3396,7 +3391,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3410,10 +3405,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45363</v>
+        <v>46171</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3426,7 +3421,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3469,7 +3464,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3479,14 +3474,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45149</v>
+        <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3498,13 +3493,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3564,7 +3554,7 @@
         <v>45120</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3637,7 +3627,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3683,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3707,10 +3697,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45109</v>
+        <v>45120</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3723,7 +3713,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3766,7 +3756,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3780,10 +3770,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44972</v>
+        <v>45149</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3795,8 +3785,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45478</v>
+        <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3868,8 +3863,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>45124</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4002,7 +4002,7 @@
         <v>46314</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4075,7 +4075,7 @@
         <v>46314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44938</v>
+        <v>46314</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4221,7 +4221,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46314</v>
+        <v>45417</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45835</v>
+        <v>45596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.9</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46171</v>
+        <v>45478</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>

--- a/Översikt VÄRMDÖ.xlsx
+++ b/Översikt VÄRMDÖ.xlsx
@@ -601,7 +601,7 @@
         <v>45196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46164</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44859</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45126</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45833</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>44257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46205</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>44544</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>44539</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31593-2025</t>
+          <t>A 20373-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45833</v>
+        <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1722,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1749,46 +1749,46 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 20373-2025</t>
+          <t>A 31593-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45775</v>
+        <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1827,10 +1827,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1854,46 +1854,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 20373-2025 artfynd.xlsx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 31593-2025 artfynd.xlsx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 20373-2025 karta.png", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 31593-2025 karta.png", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 20373-2025 georefererad karta.tif", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 31593-2025 georefererad karta.tif", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 20373-2025 FSC-klagomål.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 31593-2025 FSC-klagomål.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 20373-2025 FSC-klagomål mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 31593-2025 FSC-klagomål mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 20373-2025 tillsynsbegäran.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 31593-2025 tillsynsbegäran.docx", "A 31593-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 20373-2025 tillsynsbegäran mail.docx", "A 20373-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 31593-2025 tillsynsbegäran mail.docx", "A 31593-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54056-2022</t>
+          <t>A 33046-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44876</v>
+        <v>44785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1922,22 +1922,17 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1952,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1964,46 +1959,50 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28354-2026</t>
+          <t>A 54056-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2013,14 +2012,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46195</v>
+        <v>44876</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,8 +2031,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,10 +2070,10 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2077,38 +2081,38 @@
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 54056-2022 artfynd.xlsx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 54056-2022 karta.png", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 54056-2022 georefererad karta.tif", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 54056-2022 FSC-klagomål.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 54056-2022 FSC-klagomål mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 54056-2022 tillsynsbegäran.docx", "A 54056-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 54056-2022 tillsynsbegäran mail.docx", "A 54056-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30154-2022</t>
+          <t>A 28354-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44757</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2138,7 +2142,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2171,49 +2175,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 28354-2026 artfynd.xlsx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 28354-2026 karta.png", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 28354-2026 georefererad karta.tif", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 28354-2026 FSC-klagomål.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 28354-2026 FSC-klagomål mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 28354-2026 tillsynsbegäran.docx", "A 28354-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 28354-2026 tillsynsbegäran mail.docx", "A 28354-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33046-2022</t>
+          <t>A 30154-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2227,10 +2231,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44785</v>
+        <v>44757</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2243,16 +2247,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2267,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2283,39 +2287,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 33046-2022 artfynd.xlsx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/artfynd/A 30154-2022 artfynd.xlsx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 33046-2022 karta.png", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor/A 30154-2022 karta.png", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 33046-2022 georefererad karta.tif", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/kartor_geotiff/A 30154-2022 georefererad karta.tif", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 33046-2022 FSC-klagomål.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomål/A 30154-2022 FSC-klagomål.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 33046-2022 FSC-klagomål mail.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/klagomålsmail/A 30154-2022 FSC-klagomål mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 33046-2022 tillsynsbegäran.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsyn/A 30154-2022 tillsynsbegäran.docx", "A 30154-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 33046-2022 tillsynsbegäran mail.docx", "A 33046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0120/fåglar/A 33046-2022 prioriterade fågelarter.docx", "A 33046-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0120/tillsynsmail/A 30154-2022 tillsynsbegäran mail.docx", "A 30154-2022")</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>44539</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>44544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2240-2023</t>
+          <t>A 9966-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44938</v>
+        <v>45363</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32230-2025</t>
+          <t>A 32286-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45835</v>
+        <v>45120</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.9</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8756-2023</t>
+          <t>A 32458-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44972</v>
+        <v>45120</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30002-2023</t>
+          <t>A 32230-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45109</v>
+        <v>45835</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17623-2024</t>
+          <t>A 36148-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45417</v>
+        <v>45149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3123,8 +3123,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3167,7 +3172,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33061-2024</t>
+          <t>A 17086-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45517</v>
+        <v>45754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3196,8 +3201,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3240,7 +3250,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20053-2023</t>
+          <t>A 33958-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3250,14 +3260,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45054</v>
+        <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3269,13 +3279,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9966-2024</t>
+          <t>A 17624-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3332,10 +3337,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45363</v>
+        <v>45417</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3348,7 +3353,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3391,7 +3396,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24798-2026</t>
+          <t>A 49568-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3405,10 +3410,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46171</v>
+        <v>45596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3421,7 +3426,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3464,7 +3469,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 114-2023</t>
+          <t>A 28590-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3474,14 +3479,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44918</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3494,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3537,7 +3542,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32286-2023</t>
+          <t>A 2240-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3551,10 +3556,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45120</v>
+        <v>44938</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3567,7 +3572,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3610,7 +3615,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3827-2022</t>
+          <t>A 8756-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3624,10 +3629,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44587</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3640,7 +3645,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3683,7 +3688,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32458-2023</t>
+          <t>A 30002-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3697,10 +3702,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45120</v>
+        <v>45109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3713,7 +3718,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3756,7 +3761,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 36148-2023</t>
+          <t>A 17623-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3770,10 +3775,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45149</v>
+        <v>45417</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3785,13 +3790,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17086-2025</t>
+          <t>A 33061-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45754</v>
+        <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3863,13 +3863,8 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3912,7 +3907,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33958-2023</t>
+          <t>A 24798-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45124</v>
+        <v>46171</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3942,7 +3937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>8.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3985,7 +3980,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43301-2026</t>
+          <t>A 20053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3995,14 +3990,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46314</v>
+        <v>45054</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4014,8 +4009,13 @@
           <t>VÄRMDÖ</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 43314-2026</t>
+          <t>A 114-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4068,14 +4068,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46314</v>
+        <v>44918</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43308-2026</t>
+          <t>A 3827-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46314</v>
+        <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43287-2026</t>
+          <t>A 43301-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4221,7 +4221,7 @@
         <v>46314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17624-2024</t>
+          <t>A 43314-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45417</v>
+        <v>46314</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49568-2024</t>
+          <t>A 43308-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45596</v>
+        <v>46314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28590-2024</t>
+          <t>A 43287-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45478</v>
+        <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>45468</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45695</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45695</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>45695</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45695</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45695</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
